--- a/diseases/d029/1995-1999.xlsx
+++ b/diseases/d029/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10735,9 +10660,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11359,9 +11281,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12128,9 +12047,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12897,9 +12813,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="S64" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13666,9 +13579,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14435,9 +14345,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15204,9 +15111,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15973,9 +15877,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16742,9 +16643,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="S84" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17511,9 +17409,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18280,9 +18175,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19049,9 +18941,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19818,9 +19707,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20356,9 +20242,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="S103" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20980,9 +20863,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21749,9 +21629,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22518,9 +22395,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23287,9 +23161,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24056,9 +23927,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24825,9 +24693,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25594,9 +25459,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="S130" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26363,9 +26225,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27132,9 +26991,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27901,9 +27757,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="S142" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28670,9 +28523,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29439,9 +29289,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29977,9 +29824,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -30601,9 +30445,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -31370,9 +31211,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32139,9 +31977,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="S164" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -32908,9 +32743,6 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -33677,9 +33509,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="S172" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -34446,9 +34275,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35215,9 +35041,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -35984,9 +35807,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -36753,9 +36573,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -37522,9 +37339,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -38289,9 +38103,6 @@
         <v>0</v>
       </c>
       <c r="O196" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q196" t="n">
         <v>0</v>
       </c>
       <c r="S196" t="inlineStr">
